--- a/output/graficos_dimensiones/comunal_e_mediabrut_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mediabrut_a_2021_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:27</t>
+    <t xml:space="preserve">2026-09-10 00:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mediabrut_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mediabrut_a_2021_o higgins.xlsx
@@ -126,15 +126,15 @@
     <t xml:space="preserve">Peralillo</t>
   </si>
   <si>
+    <t xml:space="preserve">Marchigüe</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pumanque</t>
   </si>
   <si>
     <t xml:space="preserve">Lolol</t>
   </si>
   <si>
-    <t xml:space="preserve">Marchigüe</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:34</t>
+    <t xml:space="preserve">2026-09-18 10:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1084,13 +1084,13 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>6309</v>
+        <v>6204</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>98.03</v>
+        <v>98.69</v>
       </c>
     </row>
     <row r="33">
@@ -1101,13 +1101,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>6304</v>
+        <v>6309</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>97.52</v>
+        <v>98.03</v>
       </c>
     </row>
     <row r="34">
@@ -1118,10 +1118,14 @@
         <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>6204</v>
-      </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
+        <v>6304</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>97.52</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E34"/>
